--- a/output/pdf_financials_xlsx/TWY.H.xlsx
+++ b/output/pdf_financials_xlsx/TWY.H.xlsx
@@ -1180,46 +1180,46 @@
         <v>-0.081081</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.075365</v>
+        <v>-0.075365</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.079001</v>
+        <v>-0.079001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.073444</v>
+        <v>-0.073444</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.809659</v>
+        <v>-0.809659</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.116408</v>
+        <v>-0.116408</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.125177</v>
+        <v>-0.125177</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.114741</v>
+        <v>-0.114741</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.113724</v>
+        <v>-0.113724</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="17">
@@ -1448,46 +1448,46 @@
         <v>-0.081081</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.075365</v>
+        <v>-0.075365</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.079001</v>
+        <v>-0.079001</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.073444</v>
+        <v>-0.073444</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.809659</v>
+        <v>-0.809659</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.116408</v>
+        <v>-0.116408</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.125177</v>
+        <v>-0.125177</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.114741</v>
+        <v>-0.114741</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.113724</v>
+        <v>-0.113724</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="21">
@@ -1604,46 +1604,46 @@
         <v>-0.081081</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.075365</v>
+        <v>-0.075365</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.079001</v>
+        <v>-0.079001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.073444</v>
+        <v>-0.073444</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.809659</v>
+        <v>-0.809659</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.116408</v>
+        <v>-0.116408</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.125177</v>
+        <v>-0.125177</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.114741</v>
+        <v>-0.114741</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.113724</v>
+        <v>-0.113724</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="24">
@@ -1812,7 +1812,7 @@
         <v>1.35135</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.0878</v>
+        <v>2.0878</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1890,46 +1890,46 @@
         <v>-0.081081</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.078213</v>
+        <v>-0.072517</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.08060299999999999</v>
+        <v>-0.077399</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07702000000000001</v>
+        <v>-0.069868</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.811708</v>
+        <v>-0.8076100000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.117025</v>
+        <v>-0.115791</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.125327</v>
+        <v>-0.125027</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.115073</v>
+        <v>-0.114409</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.113842</v>
+        <v>-0.113606</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="28">
@@ -1994,46 +1994,46 @@
         <v>-0.081081</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.078213</v>
+        <v>-0.072517</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.08060299999999999</v>
+        <v>-0.077399</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.07702000000000001</v>
+        <v>-0.069868</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.811708</v>
+        <v>-0.8076100000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.117025</v>
+        <v>-0.115791</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.125327</v>
+        <v>-0.125027</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.115073</v>
+        <v>-0.114409</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.113842</v>
+        <v>-0.113606</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="30">
@@ -2128,46 +2128,46 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.056482</v>
+        <v>0.059124</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.002642</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -14869,7 +14869,11 @@
           <t>Warrants reserve (note 5(d))</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -15417,7 +15421,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>0.059124</v>
       </c>
@@ -26515,16 +26523,16 @@
         </is>
       </c>
       <c r="P211" s="5" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="Q211" s="5" t="n">
-        <v>0.137031</v>
+        <v>-0.137031</v>
       </c>
       <c r="R211" s="5" t="n">
-        <v>0.151931</v>
+        <v>-0.151931</v>
       </c>
       <c r="S211" s="5" t="n">
-        <v>0.160782</v>
+        <v>-0.160782</v>
       </c>
     </row>
     <row r="212">
@@ -28826,10 +28834,10 @@
         </is>
       </c>
       <c r="O237" s="5" t="n">
-        <v>0.114918</v>
+        <v>-0.114918</v>
       </c>
       <c r="P237" s="5" t="n">
-        <v>0.122066</v>
+        <v>-0.122066</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -29896,10 +29904,10 @@
         </is>
       </c>
       <c r="M249" s="5" t="n">
-        <v>0.114741</v>
+        <v>-0.114741</v>
       </c>
       <c r="N249" s="5" t="n">
-        <v>0.113724</v>
+        <v>-0.113724</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -30643,19 +30651,19 @@
         </is>
       </c>
       <c r="I258" s="5" t="n">
-        <v>0.073444</v>
+        <v>-0.073444</v>
       </c>
       <c r="J258" s="5" t="n">
-        <v>0.809659</v>
+        <v>-0.809659</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>0.116408</v>
+        <v>-0.116408</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>0.125177</v>
+        <v>-0.125177</v>
       </c>
       <c r="M258" s="5" t="n">
-        <v>0.114741</v>
+        <v>-0.114741</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -30968,10 +30976,10 @@
         </is>
       </c>
       <c r="H262" s="5" t="n">
-        <v>0.079001</v>
+        <v>-0.079001</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>0.073444</v>
+        <v>-0.073444</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -30979,10 +30987,10 @@
         </is>
       </c>
       <c r="K262" s="5" t="n">
-        <v>0.116408</v>
+        <v>-0.116408</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>0.125177</v>
+        <v>-0.125177</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
@@ -32742,13 +32750,13 @@
         </is>
       </c>
       <c r="F282" s="5" t="n">
-        <v>0.041756</v>
+        <v>-0.041756</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>0.075365</v>
+        <v>-0.075365</v>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.079001</v>
+        <v>-0.079001</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TWY.H.xlsx
+++ b/output/pdf_financials_xlsx/TWY.H.xlsx
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001209</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002542</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-0.002848</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.081081</v>
+        <v>-0.08229</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.041756</v>
+        <v>-0.039214</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.072517</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.081081</v>
+        <v>-0.08229</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.041756</v>
+        <v>-0.039214</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.072517</v>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.558716</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.52112</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.488555</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.387887</v>
@@ -2290,25 +2290,25 @@
         <v>0.19325</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07889500000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.015671</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.027095</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.011938</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.010459</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.068971</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.002458</v>
       </c>
     </row>
     <row r="35">
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.558716</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.52112</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.488555</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.387887</v>
@@ -2394,25 +2394,25 @@
         <v>0.19325</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.07889500000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.015671</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.027095</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.011938</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.010459</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.068971</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.002458</v>
       </c>
     </row>
     <row r="37">
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.564662</v>
+        <v>0.005946</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.52112</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.489286</v>
+        <v>0.000731</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.000205</v>
@@ -3018,25 +3018,25 @@
         <v>0.003293</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.08196000000000001</v>
+        <v>0.003065</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018472</v>
+        <v>0.002801</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.029346</v>
+        <v>0.002251</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.011938</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.010459</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.068971</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.002458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -33277,7 +33277,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">

--- a/output/pdf_financials_xlsx/TWY.H.xlsx
+++ b/output/pdf_financials_xlsx/TWY.H.xlsx
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.000159</v>
+        <v>0.001012</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.000665</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.00182</v>
@@ -20389,7 +20389,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -33734,7 +33738,11 @@
           <t>Office Expenses</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E293" s="5" t="n">
         <v>0.000853</v>
       </c>
@@ -34563,7 +34571,11 @@
           <t>Office expenses 853</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
